--- a/sheets/대금율보/검수/강원풍류.xlsx
+++ b/sheets/대금율보/검수/강원풍류.xlsx
@@ -8267,7 +8267,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -8275,7 +8275,7 @@
       <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 南</t>
         </is>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇‹</t>
+          <t xml:space="preserve">㒇</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -8383,7 +8383,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -8391,7 +8391,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 南</t>
         </is>
       </c>
@@ -8483,16 +8483,14 @@
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太太∧
-太仲フ
-‹</t>
+太仲フ</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -8539,8 +8537,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="K7" s="25"/>
@@ -8606,8 +8603,7 @@
       <c r="K8" s="26"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林フ
-‹</t>
+          <t xml:space="preserve">林フ</t>
         </is>
       </c>
       <c r="M8" s="26"/>
@@ -8645,7 +8641,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -8704,23 +8700,20 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㳞ʒ
-㳞フ
-‹</t>
+㳞フ</t>
         </is>
       </c>
       <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃
-㒇
-‹</t>
+㒇</t>
         </is>
       </c>
       <c r="G10" s="25"/>
@@ -8779,7 +8772,7 @@
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -8787,7 +8780,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–‹
+–
 太</t>
         </is>
       </c>
@@ -8914,7 +8907,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -8922,7 +8915,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–‹
+–
 仲</t>
         </is>
       </c>
@@ -9008,8 +9001,7 @@
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇
-‹</t>
+          <t xml:space="preserve">㒇</t>
         </is>
       </c>
       <c r="M14" s="26"/>
@@ -9055,7 +9047,7 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–‹
+–
 仲</t>
         </is>
       </c>
@@ -9091,8 +9083,7 @@
       <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="Q15" s="22"/>
@@ -9137,8 +9128,7 @@
       <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="K16" s="25"/>
@@ -9193,7 +9183,7 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–‹
+–
 太</t>
         </is>
       </c>
@@ -9213,8 +9203,7 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="M17" s="26"/>
@@ -9247,8 +9236,7 @@
       <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢南
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C18" s="22"/>
@@ -9261,8 +9249,7 @@
       <c r="E18" s="22"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="G18" s="22"/>
@@ -9322,7 +9309,7 @@
       <c r="D19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -9330,7 +9317,7 @@
       <c r="F19" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 南</t>
         </is>
       </c>
@@ -9345,8 +9332,7 @@
       <c r="J19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃㒇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K19" s="25"/>
@@ -9413,16 +9399,14 @@
       <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃㒇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M20" s="26"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="O20" s="26"/>
@@ -9459,7 +9443,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -9501,8 +9485,7 @@
       <c r="R21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲ʒ
-仲フ
-‹</t>
+仲フ</t>
         </is>
       </c>
       <c r="S21" s="22"/>
@@ -9574,16 +9557,12 @@
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="0"/>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B23" s="21"/>
       <c r="C23" s="26"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -9626,8 +9605,8 @@
       <c r="O23" s="26"/>
       <c r="P23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇㒇‹
-㒇‹</t>
+          <t xml:space="preserve">㒇㒇
+㒇</t>
         </is>
       </c>
       <c r="Q23" s="26"/>
@@ -9685,8 +9664,8 @@
       <c r="O24" s="22"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇㒇‹
-㒇‹</t>
+          <t xml:space="preserve">㒇㒇
+㒇</t>
         </is>
       </c>
       <c r="Q24" s="22"/>
@@ -9709,7 +9688,7 @@
       <c r="D25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -9810,8 +9789,8 @@
       <c r="O26" s="26"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇㒇‹
-㒇‹</t>
+          <t xml:space="preserve">㒇㒇
+㒇</t>
         </is>
       </c>
       <c r="Q26" s="26"/>

--- a/sheets/대금율보/검수/강원풍류.xlsx
+++ b/sheets/대금율보/검수/강원풍류.xlsx
@@ -8207,30 +8207,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="19.86" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="19.86" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="19.86" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="19.86" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="142.86" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="106.65" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="106.65" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="106.65" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="S5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="106.65" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="106.65" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="S7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="106.65" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="26"/>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="S8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="106.65" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="106.65" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="S10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="106.65" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="S11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="106.65" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="106.65" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="106.65" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="S14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="106.65" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="106.65" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="106.65" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="S17" s="26"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="106.65" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="106.65" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="S19" s="25"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="106.65" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="S20" s="26"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="106.65" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="S21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="106.65" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="S22" s="25"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="106.65" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="26"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="S23" s="26"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="106.65" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="S24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="106.65" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
       <c r="R25" s="21"/>
       <c r="S25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="106.65" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -9808,6 +9808,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="28"/>
 </worksheet>
 </file>